--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.03533832583686</v>
+        <v>3.58074247794849</v>
       </c>
       <c r="D2" t="n">
-        <v>21.99843456201189</v>
+        <v>3.574745616326932</v>
       </c>
       <c r="E2" t="n">
-        <v>5.658947949494046</v>
+        <v>0.9195790417927826</v>
       </c>
       <c r="F2" t="n">
-        <v>5.555712393250266</v>
+        <v>0.9028032639031682</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.396901014016716</v>
+        <v>1.364496414777717</v>
       </c>
       <c r="D3" t="n">
-        <v>8.626352389947641</v>
+        <v>1.401782263366492</v>
       </c>
       <c r="E3" t="n">
-        <v>5.658947949494046</v>
+        <v>0.9195790417927826</v>
       </c>
       <c r="F3" t="n">
-        <v>5.555712393250266</v>
+        <v>0.9028032639031682</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.07103591945525</v>
+        <v>2.124043336911479</v>
       </c>
       <c r="D4" t="n">
-        <v>13.12440474840669</v>
+        <v>2.132715771616087</v>
       </c>
       <c r="E4" t="n">
-        <v>5.658947949494046</v>
+        <v>0.9195790417927826</v>
       </c>
       <c r="F4" t="n">
-        <v>5.555712393250266</v>
+        <v>0.9028032639031682</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
